--- a/prepare/names.xlsx
+++ b/prepare/names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\KU2026Computer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026-1H609\prepare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB655533-F566-45FF-AE12-188245619386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E33E5D-9C31-40B7-AB8B-1B6A78F78032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="1575" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="88">
   <si>
     <t>権限</t>
   </si>
@@ -265,14 +265,32 @@
     <t>2571070h@stu.kobe-u.ac.jp</t>
   </si>
   <si>
-    <t>出席</t>
+    <t>Group1</t>
+  </si>
+  <si>
+    <t>出席3</t>
+  </si>
+  <si>
+    <t>出席2</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>Group2</t>
+  </si>
+  <si>
+    <t>attend4</t>
+  </si>
+  <si>
+    <t>Group4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -284,8 +302,24 @@
       <sz val="11"/>
       <name val="ＭＳ ゴシック"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,6 +329,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -348,10 +387,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -360,8 +400,14 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -694,20 +740,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
     <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="31" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -738,11 +786,29 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -771,11 +837,17 @@
       <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -804,11 +876,17 @@
       <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -839,11 +917,24 @@
       <c r="J4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -874,11 +965,24 @@
       <c r="J5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -909,11 +1013,27 @@
       <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5">
+        <v>3</v>
+      </c>
+      <c r="P6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -944,11 +1064,27 @@
       <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K7">
-        <v>1</v>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -979,11 +1115,27 @@
       <c r="J8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" s="5">
+        <v>3</v>
+      </c>
+      <c r="P8" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1014,11 +1166,29 @@
       <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K9">
-        <v>1</v>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1049,11 +1219,27 @@
       <c r="J10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K10">
-        <v>1</v>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1084,11 +1270,29 @@
       <c r="J11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2</v>
+      </c>
+      <c r="P11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1119,11 +1323,29 @@
       <c r="J12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K12">
-        <v>1</v>
+      <c r="K12" s="5">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1</v>
+      </c>
+      <c r="P12" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1154,11 +1376,27 @@
       <c r="J13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K13">
-        <v>1</v>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="5">
+        <v>1</v>
+      </c>
+      <c r="P13" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1189,8 +1427,26 @@
       <c r="J14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K14">
-        <v>1</v>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>5</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" s="5">
+        <v>3</v>
+      </c>
+      <c r="P14" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/prepare/names.xlsx
+++ b/prepare/names.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026-1H609\prepare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E33E5D-9C31-40B7-AB8B-1B6A78F78032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E922E88-C763-45CC-868C-F998C36698D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="1575" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Score" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="102">
   <si>
     <t>権限</t>
   </si>
@@ -284,13 +285,55 @@
   </si>
   <si>
     <t>Group4</t>
+  </si>
+  <si>
+    <t>attend5</t>
+  </si>
+  <si>
+    <t>Group5</t>
+  </si>
+  <si>
+    <t>attend6</t>
+  </si>
+  <si>
+    <t>Group6</t>
+  </si>
+  <si>
+    <t>attend7</t>
+  </si>
+  <si>
+    <t>Group7</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>score2</t>
+  </si>
+  <si>
+    <t>score3</t>
+  </si>
+  <si>
+    <t>score4</t>
+  </si>
+  <si>
+    <t>score5</t>
+  </si>
+  <si>
+    <t>score6</t>
+  </si>
+  <si>
+    <t>score7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -318,8 +361,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +393,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -387,27 +451,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -740,22 +808,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="25.7109375" customWidth="1"/>
     <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="31" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="14" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="20" width="9.140625" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,29 +855,47 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:23">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -837,17 +924,23 @@
       <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5"/>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:23">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -876,17 +969,23 @@
       <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5"/>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:23">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -917,24 +1016,33 @@
       <c r="J4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:23">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -965,24 +1073,33 @@
       <c r="J5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:23">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -1013,27 +1130,45 @@
       <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="5">
-        <v>1</v>
-      </c>
-      <c r="L6" s="5">
-        <v>3</v>
-      </c>
-      <c r="M6" s="5"/>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6" s="5">
-        <v>3</v>
-      </c>
-      <c r="P6" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <v>3</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4">
+        <v>1</v>
+      </c>
+      <c r="O6" s="4">
+        <v>3</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>3</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5">
+        <v>2</v>
+      </c>
+      <c r="V6" s="5">
+        <v>1</v>
+      </c>
+      <c r="W6" s="5">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:23">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1064,27 +1199,42 @@
       <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5">
-        <v>3</v>
-      </c>
-      <c r="M7" s="5"/>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5">
-        <v>2</v>
-      </c>
-      <c r="P7" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>3</v>
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4">
+        <v>2</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>3</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>2</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1</v>
+      </c>
+      <c r="U7" s="5">
+        <v>2</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:23">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1115,27 +1265,45 @@
       <c r="J8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5">
-        <v>3</v>
-      </c>
-      <c r="P8" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>1</v>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4">
+        <v>3</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>1</v>
+      </c>
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
+      </c>
+      <c r="V8" s="5">
+        <v>1</v>
+      </c>
+      <c r="W8" s="5">
+        <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:23">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1166,29 +1334,47 @@
       <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="5">
-        <v>1</v>
-      </c>
-      <c r="L9" s="5">
-        <v>1</v>
-      </c>
-      <c r="M9" s="5">
-        <v>5</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9" s="5">
-        <v>2</v>
-      </c>
-      <c r="P9" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>2</v>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4">
+        <v>5</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4">
+        <v>2</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>2</v>
+      </c>
+      <c r="R9" s="5">
+        <v>1</v>
+      </c>
+      <c r="S9" s="5">
+        <v>3</v>
+      </c>
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+      <c r="U9" s="5">
+        <v>3</v>
+      </c>
+      <c r="V9" s="5">
+        <v>1</v>
+      </c>
+      <c r="W9" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:23">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1219,27 +1405,45 @@
       <c r="J10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="5">
-        <v>1</v>
-      </c>
-      <c r="L10" s="5">
-        <v>3</v>
-      </c>
-      <c r="M10" s="5"/>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-      <c r="P10" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>2</v>
+      <c r="K10" s="4">
+        <v>1</v>
+      </c>
+      <c r="L10" s="4">
+        <v>3</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>2</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1</v>
+      </c>
+      <c r="S10" s="5">
+        <v>3</v>
+      </c>
+      <c r="T10" s="5">
+        <v>1</v>
+      </c>
+      <c r="U10" s="5">
+        <v>3</v>
+      </c>
+      <c r="V10" s="5">
+        <v>1</v>
+      </c>
+      <c r="W10" s="5">
+        <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:23">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1270,29 +1474,47 @@
       <c r="J11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="5">
-        <v>1</v>
-      </c>
-      <c r="L11" s="5">
-        <v>2</v>
-      </c>
-      <c r="M11" s="5">
-        <v>5</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11" s="5">
-        <v>2</v>
-      </c>
-      <c r="P11" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="6">
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4">
+        <v>5</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1</v>
+      </c>
+      <c r="S11" s="5">
+        <v>1</v>
+      </c>
+      <c r="T11" s="5">
+        <v>1</v>
+      </c>
+      <c r="U11" s="5">
+        <v>1</v>
+      </c>
+      <c r="V11" s="5">
+        <v>1</v>
+      </c>
+      <c r="W11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:23">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1323,29 +1545,47 @@
       <c r="J12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="5">
-        <v>1</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2</v>
-      </c>
-      <c r="M12" s="5">
-        <v>5</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1</v>
-      </c>
-      <c r="P12" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>3</v>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>5</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>3</v>
+      </c>
+      <c r="R12" s="5">
+        <v>1</v>
+      </c>
+      <c r="S12" s="5">
+        <v>2</v>
+      </c>
+      <c r="T12" s="5">
+        <v>1</v>
+      </c>
+      <c r="U12" s="5">
+        <v>1</v>
+      </c>
+      <c r="V12" s="5">
+        <v>1</v>
+      </c>
+      <c r="W12" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:23">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1376,27 +1616,42 @@
       <c r="J13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4">
+        <v>1</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1</v>
+      </c>
+      <c r="P13" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>1</v>
+      </c>
+      <c r="S13" s="5">
+        <v>1</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>1</v>
+      </c>
+      <c r="W13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:23">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1427,29 +1682,1113 @@
       <c r="J14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="5">
-        <v>1</v>
-      </c>
-      <c r="L14" s="5">
-        <v>1</v>
-      </c>
-      <c r="M14" s="5">
-        <v>5</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14" s="5">
-        <v>3</v>
-      </c>
-      <c r="P14" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>3</v>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4">
+        <v>5</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4">
+        <v>3</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>3</v>
+      </c>
+      <c r="R14" s="5">
+        <v>1</v>
+      </c>
+      <c r="S14" s="5">
+        <v>2</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>3</v>
+      </c>
+      <c r="W14" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.39400000000000002" right="0.39400000000000002" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85DB5764-A6BD-4042-8AA7-21899E57A0B0}">
+  <dimension ref="A1:AB14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:28" ht="15.75" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="15.75" thickTop="1">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="7"/>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="7"/>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="7"/>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="7"/>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7"/>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7"/>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7"/>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7"/>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7"/>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7"/>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7"/>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <v>3</v>
+      </c>
+      <c r="M6" s="7">
+        <v>5</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1</v>
+      </c>
+      <c r="O6" s="4">
+        <v>3</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="8">
+        <v>5</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5">
+        <v>3</v>
+      </c>
+      <c r="V6" s="8">
+        <v>5</v>
+      </c>
+      <c r="W6" s="5">
+        <v>1</v>
+      </c>
+      <c r="X6" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="7"/>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>5</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4">
+        <v>2</v>
+      </c>
+      <c r="P7" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>3</v>
+      </c>
+      <c r="S7" s="8">
+        <v>5</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1</v>
+      </c>
+      <c r="U7" s="5">
+        <v>2</v>
+      </c>
+      <c r="V7" s="8">
+        <v>5</v>
+      </c>
+      <c r="W7" s="5">
+        <v>1</v>
+      </c>
+      <c r="X7" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7"/>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4">
+        <v>3</v>
+      </c>
+      <c r="P8" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="8">
+        <v>5</v>
+      </c>
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
+      </c>
+      <c r="V8" s="8">
+        <v>5</v>
+      </c>
+      <c r="W8" s="5">
+        <v>1</v>
+      </c>
+      <c r="X8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="7"/>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7">
+        <v>5</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4">
+        <v>2</v>
+      </c>
+      <c r="P9" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2</v>
+      </c>
+      <c r="S9" s="8">
+        <v>5</v>
+      </c>
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+      <c r="U9" s="5">
+        <v>3</v>
+      </c>
+      <c r="V9" s="8">
+        <v>5</v>
+      </c>
+      <c r="W9" s="5">
+        <v>1</v>
+      </c>
+      <c r="X9" s="5">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="7"/>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1</v>
+      </c>
+      <c r="L10" s="4">
+        <v>3</v>
+      </c>
+      <c r="M10" s="7">
+        <v>5</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5">
+        <v>2</v>
+      </c>
+      <c r="S10" s="8">
+        <v>5</v>
+      </c>
+      <c r="T10" s="5">
+        <v>1</v>
+      </c>
+      <c r="U10" s="5">
+        <v>3</v>
+      </c>
+      <c r="V10" s="8">
+        <v>5</v>
+      </c>
+      <c r="W10" s="5">
+        <v>1</v>
+      </c>
+      <c r="X10" s="5">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="7"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
+        <v>2</v>
+      </c>
+      <c r="M11" s="7">
+        <v>5</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2</v>
+      </c>
+      <c r="P11" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1</v>
+      </c>
+      <c r="S11" s="8">
+        <v>5</v>
+      </c>
+      <c r="T11" s="5">
+        <v>1</v>
+      </c>
+      <c r="U11" s="5">
+        <v>1</v>
+      </c>
+      <c r="V11" s="8">
+        <v>5</v>
+      </c>
+      <c r="W11" s="5">
+        <v>1</v>
+      </c>
+      <c r="X11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="7"/>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>2</v>
+      </c>
+      <c r="M12" s="7">
+        <v>5</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1</v>
+      </c>
+      <c r="P12" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>1</v>
+      </c>
+      <c r="R12" s="5">
+        <v>3</v>
+      </c>
+      <c r="S12" s="8">
+        <v>5</v>
+      </c>
+      <c r="T12" s="5">
+        <v>1</v>
+      </c>
+      <c r="U12" s="5">
+        <v>2</v>
+      </c>
+      <c r="V12" s="8">
+        <v>5</v>
+      </c>
+      <c r="W12" s="5">
+        <v>1</v>
+      </c>
+      <c r="X12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="7"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>1</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1</v>
+      </c>
+      <c r="P13" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>1</v>
+      </c>
+      <c r="R13" s="5">
+        <v>2</v>
+      </c>
+      <c r="S13" s="8">
+        <v>5</v>
+      </c>
+      <c r="T13" s="5">
+        <v>1</v>
+      </c>
+      <c r="U13" s="5">
+        <v>1</v>
+      </c>
+      <c r="V13" s="8">
+        <v>5</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="7"/>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7">
+        <v>5</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4">
+        <v>3</v>
+      </c>
+      <c r="P14" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>1</v>
+      </c>
+      <c r="R14" s="5">
+        <v>3</v>
+      </c>
+      <c r="S14" s="8">
+        <v>5</v>
+      </c>
+      <c r="T14" s="5">
+        <v>1</v>
+      </c>
+      <c r="U14" s="5">
+        <v>2</v>
+      </c>
+      <c r="V14" s="8">
+        <v>5</v>
+      </c>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>